--- a/requirement_documents/Tracing_Examples/Level5Reqs.xlsx
+++ b/requirement_documents/Tracing_Examples/Level5Reqs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\christopher\RM\requirement_documents\Tracing_Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C68AF9-DC84-4CDB-BEB7-FDE2C6D5375A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7201FB3F-D945-4852-9FD0-455BEF9FB025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52290" yWindow="8655" windowWidth="24000" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47880" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -206,6 +206,18 @@
   </si>
   <si>
     <t>Verify through TM/TC packages</t>
+  </si>
+  <si>
+    <t>REQ-ASW-061</t>
+  </si>
+  <si>
+    <t>Mode Tracking</t>
+  </si>
+  <si>
+    <t>The software shall implement a Tracking procedure</t>
+  </si>
+  <si>
+    <t>REQ-INST-031</t>
   </si>
 </sst>
 </file>
@@ -532,11 +544,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" customWidth="1"/>
     <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="40.6328125" style="1" customWidth="1"/>
   </cols>
@@ -704,70 +716,87 @@
     </row>
     <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>54</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>44</v>
       </c>
     </row>
